--- a/registration_forms/030_tenant_inclusion_forum_registration--registration_forms.xlsx
+++ b/registration_forms/030_tenant_inclusion_forum_registration--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -961,8 +961,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -990,12 +990,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'event_1'}</t>
+          <t>event_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Event 1'}</t>
+          <t>Event 1</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'event_2'}</t>
+          <t>event_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Event 2'}</t>
+          <t>Event 2</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'event_3'}</t>
+          <t>event_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Event 3'}</t>
+          <t>Event 3</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'wheelchair'}</t>
+          <t>wheelchair</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Wheelchair'}</t>
+          <t>Wheelchair</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'sign_language'}</t>
+          <t>sign_language</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Sign Language'}</t>
+          <t>Sign Language</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'form_1'}</t>
+          <t>form_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Form 1'}</t>
+          <t>Form 1</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'form_2'}</t>
+          <t>form_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Form 2'}</t>
+          <t>Form 2</t>
         </is>
       </c>
     </row>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'form_3'}</t>
+          <t>form_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Form 3'}</t>
+          <t>Form 3</t>
         </is>
       </c>
     </row>
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'phone_1'}</t>
+          <t>phone_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Phone 1'}</t>
+          <t>Phone 1</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'phone_2'}</t>
+          <t>phone_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Phone 2'}</t>
+          <t>Phone 2</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'wheelchair_2'}</t>
+          <t>wheelchair_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Wheelchair 2'}</t>
+          <t>Wheelchair 2</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'sign_language_2'}</t>
+          <t>sign_language_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Sign Language 2'}</t>
+          <t>Sign Language 2</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other_2'}</t>
+          <t>other_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other 2'}</t>
+          <t>Other 2</t>
         </is>
       </c>
     </row>
